--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104761_W34.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104761_W34.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6644</v>
+        <v>6.9954</v>
       </c>
       <c r="E2" t="n">
-        <v>5.646</v>
+        <v>5.8829</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0184</v>
+        <v>1.1125</v>
       </c>
       <c r="G2" t="n">
         <v>7.3013</v>
@@ -610,13 +610,13 @@
         <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0255</v>
+        <v>0.3055</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2505</v>
+        <v>0.4874</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.276</v>
+        <v>-0.1819</v>
       </c>
       <c r="V2" t="n">
         <v>0.07140000000000001</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2516</v>
+        <v>6.5269</v>
       </c>
       <c r="E3" t="n">
-        <v>7.076</v>
+        <v>7.1945</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8244</v>
+        <v>-0.6676</v>
       </c>
       <c r="G3" t="n">
         <v>3.2945</v>
@@ -688,13 +688,13 @@
         <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4204</v>
+        <v>-0.1451</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.098</v>
+        <v>0.0205</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3224</v>
+        <v>-0.1656</v>
       </c>
       <c r="V3" t="n">
         <v>4.5157</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4128</v>
+        <v>3.1272</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8936</v>
+        <v>2.4198</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5192</v>
+        <v>0.7074</v>
       </c>
       <c r="G4" t="n">
         <v>1.145</v>
@@ -766,13 +766,13 @@
         <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4272</v>
+        <v>0.1416</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.3573</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4039</v>
+        <v>-0.2157</v>
       </c>
       <c r="V4" t="n">
         <v>0.7025</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0011</v>
+        <v>0.1487</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0352</v>
+        <v>0.0832</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0341</v>
+        <v>0.0655</v>
       </c>
       <c r="G5" t="n">
         <v>0.1359</v>
@@ -844,13 +844,13 @@
         <v>0.2276</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3646</v>
+        <v>-0.2148</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0697</v>
+        <v>0.0487</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2949</v>
+        <v>-0.2636</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ARANITOVIC</t>
+          <t>D. MAVRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0331</v>
+        <v>-1.2468</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4482</v>
+        <v>-0.0225</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4151</v>
+        <v>-1.2243</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.5615</v>
+        <v>1.3418</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.0656</v>
+        <v>0.2157</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.4958</v>
+        <v>1.1261</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.0161</v>
+        <v>3.9637</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.3897</v>
+        <v>1.1786</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6264999999999999</v>
+        <v>2.7851</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5453</v>
+        <v>-2.6219</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.9629</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8694</v>
+        <v>-1.659</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2763</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2763</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>3.2733</v>
+        <v>-0.9268999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3419</v>
+        <v>-0.5718</v>
       </c>
       <c r="U6" t="n">
-        <v>1.9314</v>
+        <v>-0.3551</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.0212</v>
+        <v>0.387</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7739</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2472</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3085</v>
+        <v>-1.7439</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7027</v>
+        <v>0.1105</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0112</v>
+        <v>-1.8544</v>
       </c>
       <c r="G7" t="n">
         <v>-2.0121</v>
@@ -1000,13 +1000,13 @@
         <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2483</v>
+        <v>-0.1871</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7428</v>
+        <v>0.1506</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4945</v>
+        <v>-0.3377</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. BRANKOVIC</t>
+          <t>A. KURUCS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8665</v>
+        <v>-2.02</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4779</v>
+        <v>-1.9115</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.3444</v>
+        <v>-0.1086</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4318</v>
+        <v>-2.1616</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6543</v>
+        <v>-1.4451</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2225</v>
+        <v>-0.7165</v>
       </c>
       <c r="J8" t="n">
-        <v>2.5932</v>
+        <v>-2.0621</v>
       </c>
       <c r="K8" t="n">
-        <v>2.258</v>
+        <v>-1.4586</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3351</v>
+        <v>-0.6035</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1613</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6037</v>
+        <v>0.0135</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5576</v>
+        <v>-0.113</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4553</v>
+        <v>1.3658</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1382</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5934</v>
+        <v>1.3658</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1279</v>
+        <v>-0.1348</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0229</v>
+        <v>0.1506</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1049</v>
+        <v>-0.2854</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.8814</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.8814</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. MAVRA</t>
+          <t>D. BRANKOVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0342</v>
+        <v>-2.0791</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4963</v>
+        <v>1.3595</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5379</v>
+        <v>-3.4385</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3418</v>
+        <v>0.4318</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2157</v>
+        <v>1.6543</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1261</v>
+        <v>-1.2225</v>
       </c>
       <c r="J9" t="n">
-        <v>3.9637</v>
+        <v>2.5932</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1786</v>
+        <v>2.258</v>
       </c>
       <c r="L9" t="n">
-        <v>2.7851</v>
+        <v>0.3351</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.6219</v>
+        <v>-2.1613</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9629</v>
+        <v>-0.6037</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.659</v>
+        <v>-1.5576</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.0487</v>
+        <v>0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.4145</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3658</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.7143</v>
+        <v>-0.0847</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0455</v>
+        <v>-0.0955</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6688</v>
+        <v>0.0108</v>
       </c>
       <c r="V9" t="n">
-        <v>0.387</v>
+        <v>-2.8814</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.387</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. KURUCS</t>
+          <t>A. ARANITOVIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0374</v>
+        <v>-2.4478</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7406</v>
+        <v>-2.5142</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2968</v>
+        <v>0.0664</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1616</v>
+        <v>-3.5615</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4451</v>
+        <v>-2.0656</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7165</v>
+        <v>-1.4958</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.0621</v>
+        <v>-2.0161</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.4586</v>
+        <v>-1.3897</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6035</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-1.5453</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0135</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.113</v>
+        <v>-0.8694</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3658</v>
+        <v>2.2763</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3658</v>
+        <v>2.2763</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1521</v>
+        <v>0.8585</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6785</v>
+        <v>0.2759</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4736</v>
+        <v>0.5826</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0895</v>
+        <v>-2.0212</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0895</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. WALKER</t>
+          <t>M. ANDRIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9888</v>
+        <v>-3.5544</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2938</v>
+        <v>-3.456</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.695</v>
+        <v>-0.0984</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0887</v>
+        <v>-3.1953</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0433</v>
+        <v>-0.7673</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0454</v>
+        <v>-2.4281</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.527</v>
+        <v>-2.2801</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3447</v>
+        <v>-0.1346</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.8718</v>
+        <v>-2.1455</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5617</v>
+        <v>-0.9152</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3881</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1736</v>
+        <v>-0.2826</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6829</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4553</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0301</v>
+        <v>-0.2892</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3714</v>
+        <v>-0.1955</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3413</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2472</v>
+        <v>0.1578</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2472</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. ANDRIC</t>
+          <t>J. WALKER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4846</v>
+        <v>-4.1316</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1667</v>
+        <v>-1.5307</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3179</v>
+        <v>-2.6009</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.1953</v>
+        <v>-2.0887</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7673</v>
+        <v>-0.0433</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.4281</v>
+        <v>-2.0454</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.2801</v>
+        <v>-0.527</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1346</v>
+        <v>0.3447</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.1455</v>
+        <v>-0.8718</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9152</v>
+        <v>-1.5617</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.3881</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2826</v>
+        <v>-1.1736</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2276</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9105</v>
+        <v>0.4553</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2194</v>
+        <v>-0.1127</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9061</v>
+        <v>0.1345</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3133</v>
+        <v>-0.2473</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1578</v>
+        <v>-1.2472</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1578</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4253999999999998</v>
+        <v>-0.4253999999999984</v>
       </c>
       <c r="E13" t="n">
-        <v>7.6154</v>
+        <v>7.615500000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.040799999999999</v>
+        <v>-8.040900000000001</v>
       </c>
       <c r="G13" t="n">
         <v>0.6310999999999991</v>
@@ -1456,7 +1456,7 @@
         <v>-5.5366</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.425300000000002</v>
+        <v>-9.4253</v>
       </c>
       <c r="P13" t="n">
         <v>1.1382</v>
@@ -1468,13 +1468,13 @@
         <v>14.796</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7894999999999999</v>
+        <v>-0.7897</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7627999999999998</v>
+        <v>0.7627000000000002</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5524</v>
+        <v>-1.5526</v>
       </c>
       <c r="V13" t="n">
         <v>-1.404900000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6592</v>
+        <v>4.3293</v>
       </c>
       <c r="E14" t="n">
-        <v>6.8704</v>
+        <v>7.2257</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.2112</v>
+        <v>-2.8964</v>
       </c>
       <c r="G14" t="n">
         <v>3.6521</v>
@@ -1546,13 +1546,13 @@
         <v>1.8211</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5086000000000001</v>
+        <v>0.1615</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1111</v>
+        <v>0.4665</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6198</v>
+        <v>-0.305</v>
       </c>
       <c r="V14" t="n">
         <v>2.3367</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. ROBINSON</t>
+          <t>J. WRIGHT-FOREMAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2877</v>
+        <v>1.295</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1231</v>
+        <v>0.9235</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1645</v>
+        <v>0.3715</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.0482</v>
+        <v>1.2079</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.723</v>
+        <v>-0.3471</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3252</v>
+        <v>1.555</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5057</v>
+        <v>2.1086</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5353</v>
+        <v>0.1132</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0296</v>
+        <v>1.9955</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5425</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1877</v>
+        <v>-0.4603</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3548</v>
+        <v>-0.4405</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9105</v>
+        <v>0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.3658</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2763</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4936</v>
+        <v>-0.1405</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9052</v>
+        <v>-0.2047</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5885</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9317</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0895</v>
+        <v>0.1578</v>
       </c>
       <c r="X15" t="n">
         <v>-0.1578</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0627</v>
+        <v>0.8188</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5773</v>
+        <v>-0.6957</v>
       </c>
       <c r="F16" t="n">
-        <v>1.64</v>
+        <v>1.5145</v>
       </c>
       <c r="G16" t="n">
         <v>-1.359</v>
@@ -1702,13 +1702,13 @@
         <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>0.669</v>
+        <v>0.425</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1808</v>
+        <v>0.0624</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4881</v>
+        <v>0.3627</v>
       </c>
       <c r="V16" t="n">
         <v>0.387</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. WRIGHT-FOREMAN</t>
+          <t>T. BELL-HAYNES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7271</v>
+        <v>0.4738</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4497</v>
+        <v>2.0322</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2774</v>
+        <v>-1.5585</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2079</v>
+        <v>3.1272</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3471</v>
+        <v>1.5196</v>
       </c>
       <c r="I17" t="n">
-        <v>1.555</v>
+        <v>1.6075</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1086</v>
+        <v>5.0436</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1132</v>
+        <v>1.5061</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9955</v>
+        <v>3.5375</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-1.9164</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4603</v>
+        <v>0.0135</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4405</v>
+        <v>-1.93</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2276</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1382</v>
+        <v>-3.6421</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3658</v>
+        <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7084</v>
+        <v>-0.2162</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6785</v>
+        <v>0.1574</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0299</v>
+        <v>-0.3736</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.6162</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1578</v>
+        <v>0.4733</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1578</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. BELL-HAYNES</t>
+          <t>D. ROBINSON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1136</v>
+        <v>0.3271</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2691</v>
+        <v>-0.5876</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1555</v>
+        <v>0.9147</v>
       </c>
       <c r="G18" t="n">
-        <v>3.1272</v>
+        <v>-2.0482</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5196</v>
+        <v>-0.723</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6075</v>
+        <v>-1.3252</v>
       </c>
       <c r="J18" t="n">
-        <v>5.0436</v>
+        <v>-0.5057</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5061</v>
+        <v>-0.5353</v>
       </c>
       <c r="L18" t="n">
-        <v>3.5375</v>
+        <v>0.0296</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9164</v>
+        <v>-1.5425</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0135</v>
+        <v>-0.1877</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.93</v>
+        <v>-1.3548</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.8211</v>
+        <v>0.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.6421</v>
+        <v>-1.3658</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8211</v>
+        <v>2.2763</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5763</v>
+        <v>0.5331</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3943</v>
+        <v>0.1945</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9707</v>
+        <v>0.3386</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6162</v>
+        <v>0.9317</v>
       </c>
       <c r="W18" t="n">
-        <v>0.4733</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0895</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1346</v>
+        <v>-0.1941</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7023</v>
+        <v>-0.2285</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5677</v>
+        <v>0.0344</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0338</v>
@@ -1936,13 +1936,13 @@
         <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2163</v>
+        <v>0.1568</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.697</v>
+        <v>-0.2232</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9133</v>
+        <v>0.3801</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4849</v>
+        <v>-0.9609</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2595</v>
+        <v>0.3119</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7443</v>
+        <v>-1.2728</v>
       </c>
       <c r="G20" t="n">
         <v>-1.0142</v>
@@ -2014,13 +2014,13 @@
         <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5294</v>
+        <v>0.0534</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3931</v>
+        <v>0.4455</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8637</v>
+        <v>-0.3921</v>
       </c>
       <c r="V20" t="n">
         <v>-0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>S. YUSTA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2986</v>
+        <v>-1.2489</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2121</v>
+        <v>0.3043</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5107</v>
+        <v>-1.5533</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0591</v>
+        <v>-1.2365</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9564</v>
+        <v>1.3957</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1027</v>
+        <v>-2.6322</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4736</v>
+        <v>1.4825</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7552</v>
+        <v>2.0717</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2288</v>
+        <v>-0.5891999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5328</v>
+        <v>-2.7189</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2012</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3315</v>
+        <v>-2.043</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2276</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2276</v>
+        <v>1.8211</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6224</v>
+        <v>-0.1522</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7385</v>
+        <v>0.1877</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1161</v>
+        <v>-0.3399</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0895</v>
+        <v>-0.3155</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0895</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. DUBLJEVIC</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4519</v>
+        <v>-1.7097</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.865</v>
+        <v>0.7383</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4131</v>
+        <v>-2.448</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8673999999999999</v>
+        <v>-1.0591</v>
       </c>
       <c r="H22" t="n">
-        <v>0.09180000000000001</v>
+        <v>-0.9564</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9592000000000001</v>
+        <v>-0.1027</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3203</v>
+        <v>0.4736</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3652</v>
+        <v>-0.7552</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0449</v>
+        <v>1.2288</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1877</v>
+        <v>-1.5328</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2734</v>
+        <v>-0.2012</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9143</v>
+        <v>-1.3315</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.3658</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2763</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9105</v>
+        <v>0.2276</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0105</v>
+        <v>0.2113</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3202</v>
+        <v>0.2647</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6903</v>
+        <v>-0.0534</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2292</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.2292</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. YUSTA</t>
+          <t>B. DUBLJEVIC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0548</v>
+        <v>-1.9154</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9986</v>
+        <v>-1.9834</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0562</v>
+        <v>0.068</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.2365</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>1.3957</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.6322</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>1.4825</v>
+        <v>0.3203</v>
       </c>
       <c r="K23" t="n">
-        <v>2.0717</v>
+        <v>0.3652</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5891999999999999</v>
+        <v>-0.0449</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.7189</v>
+        <v>-1.1877</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.2734</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.043</v>
+        <v>-0.9143</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4553</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.3658</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8211</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.9581</v>
+        <v>0.547</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1152</v>
+        <v>0.2018</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8428</v>
+        <v>0.3452</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3155</v>
+        <v>-0.2292</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.2292</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4254999999999987</v>
+        <v>1.215</v>
       </c>
       <c r="E24" t="n">
-        <v>8.040699999999999</v>
+        <v>8.040700000000003</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.6152</v>
+        <v>-6.825900000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6309999999999998</v>
+        <v>-0.6310000000000002</v>
       </c>
       <c r="H24" t="n">
         <v>1.7959</v>
@@ -2305,7 +2305,7 @@
         <v>5.5367</v>
       </c>
       <c r="L24" t="n">
-        <v>9.4254</v>
+        <v>9.425399999999998</v>
       </c>
       <c r="M24" t="n">
         <v>-15.5928</v>
@@ -2326,13 +2326,13 @@
         <v>13.658</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7897999999999996</v>
+        <v>1.5792</v>
       </c>
       <c r="T24" t="n">
-        <v>1.5525</v>
+        <v>1.5526</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7627999999999998</v>
+        <v>0.02680000000000005</v>
       </c>
       <c r="V24" t="n">
         <v>1.405</v>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104761_W34.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104761_W34.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.07140000000000001</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104761_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104761_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104761_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104761_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104761_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104761_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104761_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104761_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104761_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104761_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104761_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-6.322500000000001</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104761_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104761_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104761_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104761_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104761_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104761_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104761_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104761_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104761_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104761_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-4.9175</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
